--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -461,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,90 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.69628</v>
+        <v>17.06693</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6401</v>
+        <v>16.35267</v>
       </c>
       <c r="E2" t="n">
-        <v>16.55861</v>
+        <v>16.46351</v>
       </c>
       <c r="F2" t="n">
-        <v>56.01593</v>
+        <v>42.44695</v>
       </c>
       <c r="G2" t="n">
-        <v>42.336</v>
+        <v>0.0507</v>
       </c>
       <c r="H2" t="n">
-        <v>85.79434999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.05086</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.80199</v>
+        <v>1.80286</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.77849</v>
+        <v>16.78495</v>
       </c>
       <c r="D3" t="n">
-        <v>16.28077</v>
+        <v>16.12463</v>
       </c>
       <c r="E3" t="n">
-        <v>16.41321</v>
+        <v>16.54731</v>
       </c>
       <c r="F3" t="n">
-        <v>55.64006</v>
+        <v>42.03619</v>
       </c>
       <c r="G3" t="n">
-        <v>42.1175</v>
+        <v>0.05021</v>
       </c>
       <c r="H3" t="n">
-        <v>85.28804</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.04986</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.80896</v>
+        <v>1.7828</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.82992</v>
+        <v>16.73419</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59402</v>
+        <v>15.95835</v>
       </c>
       <c r="E4" t="n">
-        <v>16.82717</v>
+        <v>16.53667</v>
       </c>
       <c r="F4" t="n">
-        <v>55.92542</v>
+        <v>43.05781</v>
       </c>
       <c r="G4" t="n">
-        <v>42.19679</v>
+        <v>0.05151</v>
       </c>
       <c r="H4" t="n">
-        <v>85.09202000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05097</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.80844</v>
+        <v>1.79688</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.00935</v>
+        <v>16.9804</v>
       </c>
       <c r="D5" t="n">
-        <v>16.62476</v>
+        <v>15.99586</v>
       </c>
       <c r="E5" t="n">
-        <v>16.37686</v>
+        <v>16.14539</v>
       </c>
       <c r="F5" t="n">
-        <v>55.74703</v>
+        <v>42.93671</v>
       </c>
       <c r="G5" t="n">
-        <v>42.19406</v>
+        <v>0.0506</v>
       </c>
       <c r="H5" t="n">
-        <v>84.39061</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05021</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.85861</v>
+        <v>1.80757</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.47609</v>
+        <v>16.63094</v>
       </c>
       <c r="D6" t="n">
-        <v>16.47559</v>
+        <v>16.47351</v>
       </c>
       <c r="E6" t="n">
-        <v>16.70314</v>
+        <v>16.5981</v>
       </c>
       <c r="F6" t="n">
-        <v>56.56224</v>
+        <v>42.57588</v>
       </c>
       <c r="G6" t="n">
-        <v>42.71873</v>
+        <v>0.05003</v>
       </c>
       <c r="H6" t="n">
-        <v>84.35456000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.04926</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.81031</v>
+        <v>1.79599</v>
       </c>
     </row>
     <row r="7">
@@ -625,677 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.60685</v>
+        <v>17.14567</v>
       </c>
       <c r="D7" t="n">
-        <v>16.58977</v>
+        <v>16.49745</v>
       </c>
       <c r="E7" t="n">
-        <v>16.89239</v>
+        <v>16.62901</v>
       </c>
       <c r="F7" t="n">
-        <v>55.37413</v>
+        <v>42.62206</v>
       </c>
       <c r="G7" t="n">
-        <v>41.85655</v>
+        <v>0.05056</v>
       </c>
       <c r="H7" t="n">
-        <v>84.53493</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.05057</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.77225</v>
+        <v>1.77996</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.06026</v>
+        <v>16.89882</v>
       </c>
       <c r="D8" t="n">
-        <v>16.72521</v>
+        <v>16.53993</v>
       </c>
       <c r="E8" t="n">
-        <v>16.6871</v>
+        <v>16.67241</v>
       </c>
       <c r="F8" t="n">
-        <v>54.9384</v>
+        <v>41.79424</v>
       </c>
       <c r="G8" t="n">
-        <v>41.93101</v>
+        <v>0.0506</v>
       </c>
       <c r="H8" t="n">
-        <v>85.90331999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.04951</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.85464</v>
+        <v>1.81986</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.79344</v>
+        <v>16.78553</v>
       </c>
       <c r="D9" t="n">
-        <v>16.58196</v>
+        <v>16.12921</v>
       </c>
       <c r="E9" t="n">
-        <v>16.25911</v>
+        <v>16.53626</v>
       </c>
       <c r="F9" t="n">
-        <v>55.68748</v>
+        <v>42.21483</v>
       </c>
       <c r="G9" t="n">
-        <v>42.6778</v>
+        <v>0.04943</v>
       </c>
       <c r="H9" t="n">
-        <v>84.00913</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.04969</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.83012</v>
+        <v>1.76894</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.84914</v>
+        <v>16.86816</v>
       </c>
       <c r="D10" t="n">
-        <v>16.71413</v>
+        <v>16.40665</v>
       </c>
       <c r="E10" t="n">
-        <v>16.44258</v>
+        <v>16.7625</v>
       </c>
       <c r="F10" t="n">
-        <v>55.79943</v>
+        <v>41.54333</v>
       </c>
       <c r="G10" t="n">
-        <v>42.63557</v>
+        <v>0.04989</v>
       </c>
       <c r="H10" t="n">
-        <v>84.41813999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.05002</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.826</v>
+        <v>1.81784</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Outer Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Inner Radius</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.8399</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.63598</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.79527</v>
+      </c>
+      <c r="F11" t="n">
+        <v>41.98056</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05037</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.80408</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.70854</v>
+        <v>16.63394</v>
       </c>
       <c r="D12" t="n">
-        <v>16.30898</v>
+        <v>16.54446</v>
       </c>
       <c r="E12" t="n">
-        <v>16.58077</v>
+        <v>16.63079</v>
       </c>
       <c r="F12" t="n">
-        <v>54.30795</v>
+        <v>42.22655</v>
       </c>
       <c r="G12" t="n">
-        <v>41.79067</v>
+        <v>0.04975</v>
       </c>
       <c r="H12" t="n">
-        <v>83.84472</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.05064</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.83463</v>
+        <v>1.79126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.57901</v>
+        <v>16.75147</v>
       </c>
       <c r="D13" t="n">
-        <v>16.45102</v>
+        <v>16.23979</v>
       </c>
       <c r="E13" t="n">
-        <v>16.69593</v>
+        <v>16.62307</v>
       </c>
       <c r="F13" t="n">
-        <v>56.12107</v>
+        <v>42.2686</v>
       </c>
       <c r="G13" t="n">
-        <v>41.89781</v>
+        <v>0.0505</v>
       </c>
       <c r="H13" t="n">
-        <v>84.18168</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.04912</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.8108</v>
+        <v>1.80693</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.80929</v>
+        <v>16.43764</v>
       </c>
       <c r="D14" t="n">
-        <v>16.3554</v>
+        <v>16.11032</v>
       </c>
       <c r="E14" t="n">
-        <v>16.62643</v>
+        <v>16.42782</v>
       </c>
       <c r="F14" t="n">
-        <v>56.14762</v>
+        <v>41.48986</v>
       </c>
       <c r="G14" t="n">
-        <v>41.76093</v>
+        <v>0.0496</v>
       </c>
       <c r="H14" t="n">
-        <v>82.74509999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.05082</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.79397</v>
+        <v>1.834</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.4257</v>
+        <v>16.78705</v>
       </c>
       <c r="D15" t="n">
-        <v>16.42138</v>
+        <v>16.45841</v>
       </c>
       <c r="E15" t="n">
-        <v>16.4165</v>
+        <v>16.47951</v>
       </c>
       <c r="F15" t="n">
-        <v>54.45471</v>
+        <v>42.11293</v>
       </c>
       <c r="G15" t="n">
-        <v>42.37365</v>
+        <v>0.04991</v>
       </c>
       <c r="H15" t="n">
-        <v>84.64615999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.05008</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.84508</v>
+        <v>1.79452</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.40136</v>
+        <v>16.91113</v>
       </c>
       <c r="D16" t="n">
-        <v>16.38564</v>
+        <v>16.59324</v>
       </c>
       <c r="E16" t="n">
-        <v>16.4596</v>
+        <v>16.66057</v>
       </c>
       <c r="F16" t="n">
-        <v>53.65423</v>
+        <v>42.9363</v>
       </c>
       <c r="G16" t="n">
-        <v>42.65785</v>
+        <v>0.05005</v>
       </c>
       <c r="H16" t="n">
-        <v>84.39727000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.04866</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.78247</v>
+        <v>1.79652</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.10055</v>
+        <v>16.81012</v>
       </c>
       <c r="D17" t="n">
-        <v>16.48881</v>
+        <v>16.11825</v>
       </c>
       <c r="E17" t="n">
-        <v>16.4072</v>
+        <v>16.58475</v>
       </c>
       <c r="F17" t="n">
-        <v>55.5078</v>
+        <v>41.25695</v>
       </c>
       <c r="G17" t="n">
-        <v>41.71668</v>
+        <v>0.05061</v>
       </c>
       <c r="H17" t="n">
-        <v>84.75413</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.04996</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.82102</v>
+        <v>1.81989</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.76106</v>
+        <v>16.74185</v>
       </c>
       <c r="D18" t="n">
-        <v>16.51495</v>
+        <v>16.37653</v>
       </c>
       <c r="E18" t="n">
-        <v>16.37366</v>
+        <v>16.53124</v>
       </c>
       <c r="F18" t="n">
-        <v>55.41201</v>
+        <v>42.24612</v>
       </c>
       <c r="G18" t="n">
-        <v>41.67082</v>
+        <v>0.04977</v>
       </c>
       <c r="H18" t="n">
-        <v>84.88881000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.05077</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.81306</v>
+        <v>1.81519</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.62645</v>
+        <v>16.47816</v>
       </c>
       <c r="D19" t="n">
-        <v>16.47888</v>
+        <v>16.2552</v>
       </c>
       <c r="E19" t="n">
-        <v>16.80005</v>
+        <v>16.30737</v>
       </c>
       <c r="F19" t="n">
-        <v>55.74405</v>
+        <v>43.34727</v>
       </c>
       <c r="G19" t="n">
-        <v>41.60936</v>
+        <v>0.05014</v>
       </c>
       <c r="H19" t="n">
-        <v>84.30534</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.05046</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.79997</v>
+        <v>1.81754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.78019</v>
+        <v>16.74943</v>
       </c>
       <c r="D20" t="n">
-        <v>16.37647</v>
+        <v>16.60761</v>
       </c>
       <c r="E20" t="n">
-        <v>16.41591</v>
+        <v>16.70547</v>
       </c>
       <c r="F20" t="n">
-        <v>54.54398</v>
+        <v>42.25259</v>
       </c>
       <c r="G20" t="n">
-        <v>42.07103</v>
+        <v>0.05041</v>
       </c>
       <c r="H20" t="n">
-        <v>84.80736</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05054</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.80733</v>
+        <v>1.80948</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16.9449</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.46716</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.79381</v>
+      </c>
+      <c r="F21" t="n">
+        <v>41.87027</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.04894</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.8296</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
+          <t>Unit 21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.63556</v>
+        <v>16.90733</v>
       </c>
       <c r="D22" t="n">
-        <v>16.07954</v>
+        <v>16.61174</v>
       </c>
       <c r="E22" t="n">
-        <v>16.26353</v>
+        <v>16.78447</v>
       </c>
       <c r="F22" t="n">
-        <v>21.26818</v>
+        <v>42.8383</v>
       </c>
       <c r="G22" t="n">
-        <v>34.02111</v>
+        <v>0.04997</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.8115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.87941</v>
+        <v>17.11549</v>
       </c>
       <c r="D23" t="n">
-        <v>16.08477</v>
+        <v>16.62035</v>
       </c>
       <c r="E23" t="n">
-        <v>16.54305</v>
+        <v>16.83869</v>
       </c>
       <c r="F23" t="n">
-        <v>22.10932</v>
+        <v>42.27274</v>
       </c>
       <c r="G23" t="n">
-        <v>34.46969</v>
+        <v>0.05103</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.7855</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 23</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.60815</v>
+        <v>16.60746</v>
       </c>
       <c r="D24" t="n">
-        <v>15.59873</v>
+        <v>16.35265</v>
       </c>
       <c r="E24" t="n">
-        <v>16.0541</v>
+        <v>16.50268</v>
       </c>
       <c r="F24" t="n">
-        <v>21.44184</v>
+        <v>42.23895</v>
       </c>
       <c r="G24" t="n">
-        <v>33.95343</v>
+        <v>0.05019</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.82865</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 24</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.40989</v>
+        <v>16.74405</v>
       </c>
       <c r="D25" t="n">
-        <v>15.8282</v>
+        <v>16.12111</v>
       </c>
       <c r="E25" t="n">
-        <v>16.25052</v>
+        <v>16.50868</v>
       </c>
       <c r="F25" t="n">
-        <v>21.92986</v>
+        <v>42.64353</v>
       </c>
       <c r="G25" t="n">
-        <v>34.67423</v>
+        <v>0.05144</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.77484</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.43153</v>
+        <v>16.87425</v>
       </c>
       <c r="D26" t="n">
-        <v>15.79694</v>
+        <v>16.36809</v>
       </c>
       <c r="E26" t="n">
-        <v>16.21468</v>
+        <v>16.38734</v>
       </c>
       <c r="F26" t="n">
-        <v>21.74552</v>
+        <v>41.8256</v>
       </c>
       <c r="G26" t="n">
-        <v>34.63201</v>
+        <v>0.05085</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.82794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 26</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.09048</v>
+        <v>16.73349</v>
       </c>
       <c r="D27" t="n">
-        <v>15.91929</v>
+        <v>16.4794</v>
       </c>
       <c r="E27" t="n">
-        <v>16.45624</v>
+        <v>16.63349</v>
       </c>
       <c r="F27" t="n">
-        <v>21.53063</v>
+        <v>42.19572</v>
       </c>
       <c r="G27" t="n">
-        <v>33.89509</v>
+        <v>0.05021</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.85873</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.68296</v>
+        <v>17.01955</v>
       </c>
       <c r="D28" t="n">
-        <v>15.99822</v>
+        <v>16.36717</v>
       </c>
       <c r="E28" t="n">
-        <v>16.02581</v>
+        <v>16.56959</v>
       </c>
       <c r="F28" t="n">
-        <v>21.81471</v>
+        <v>41.4997</v>
       </c>
       <c r="G28" t="n">
-        <v>34.3251</v>
+        <v>0.05085</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.84626</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 28</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.69442</v>
+        <v>16.75774</v>
       </c>
       <c r="D29" t="n">
-        <v>16.00605</v>
+        <v>16.56051</v>
       </c>
       <c r="E29" t="n">
-        <v>16.1768</v>
+        <v>16.68862</v>
       </c>
       <c r="F29" t="n">
-        <v>21.91317</v>
+        <v>42.56814</v>
       </c>
       <c r="G29" t="n">
-        <v>34.00835</v>
+        <v>0.04994</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.77998</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.79543</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.39401</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.68941</v>
+      </c>
+      <c r="F30" t="n">
+        <v>41.29973</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.04998</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.80457</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>16.56616</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.39169</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.52075</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42.16139</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05047</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.83089</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.76386</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.24858</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.27376</v>
+      </c>
+      <c r="F32" t="n">
+        <v>41.38134</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.85721</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.79496</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.33023</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.73986</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.03889</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.82949</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.66945</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.4654</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.6114</v>
+      </c>
+      <c r="F34" t="n">
+        <v>41.83024</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05114</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.82537</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.78793</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.52199</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.62994</v>
+      </c>
+      <c r="F35" t="n">
+        <v>41.98206</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.82868</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.04669</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.66126</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.97612</v>
+      </c>
+      <c r="F36" t="n">
+        <v>41.55759</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.8125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.86151</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.54906</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.76045</v>
+      </c>
+      <c r="F37" t="n">
+        <v>43.05344</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.81396</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.57303</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15.83846</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.38414</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.52725</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.1381</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.60083</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.03246</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.53827</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.95303</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.71768</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>16.64775</v>
-      </c>
-      <c r="D30" t="n">
-        <v>15.98847</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16.10368</v>
-      </c>
-      <c r="F30" t="n">
-        <v>22.00289</v>
-      </c>
-      <c r="G30" t="n">
-        <v>34.04642</v>
+      <c r="C41" t="n">
+        <v>16.75594</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15.66337</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.49883</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21.609</v>
+      </c>
+      <c r="G41" t="n">
+        <v>33.49055</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.70621</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.89219</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15.9335</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.9359</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.16609</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.45479</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.63993</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.32093</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.6085</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.54882</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.79977</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.97476</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.4022</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.51235</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.97439</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.41411</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.2385</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.44726</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.14949</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.54591</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.88521</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.23149</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.97184</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.34055</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.62642</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.90494</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.11113</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.71399</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.67927</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.21292</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.83531</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.04429</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.22555</v>
+      </c>
+      <c r="G48" t="n">
+        <v>33.96302</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.62933</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.13032</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.24276</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.29024</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.17278</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.52517</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.84657</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.51898</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.68612</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.08702</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16.96425</v>
+      </c>
+      <c r="D51" t="n">
+        <v>15.95107</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.0836</v>
+      </c>
+      <c r="F51" t="n">
+        <v>21.6433</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34.59095</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.41883</v>
+      </c>
+      <c r="D52" t="n">
+        <v>15.96638</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.21805</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.72689</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34.05395</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.52713</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15.90731</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.26271</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.54287</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34.96015</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16.77257</v>
+      </c>
+      <c r="D54" t="n">
+        <v>15.92603</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.38286</v>
+      </c>
+      <c r="F54" t="n">
+        <v>21.45282</v>
+      </c>
+      <c r="G54" t="n">
+        <v>34.48088</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17.07126</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.05817</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.34687</v>
+      </c>
+      <c r="F55" t="n">
+        <v>21.66073</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.38605</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.56081</v>
+      </c>
+      <c r="D56" t="n">
+        <v>15.96857</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.41595</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.58774</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.44757</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.8214</v>
+      </c>
+      <c r="D57" t="n">
+        <v>15.97683</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.37055</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21.53264</v>
+      </c>
+      <c r="G57" t="n">
+        <v>34.00254</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.52899</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.05771</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.35288</v>
+      </c>
+      <c r="F58" t="n">
+        <v>21.60459</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.52265</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.74987</v>
+      </c>
+      <c r="D59" t="n">
+        <v>15.92027</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.1622</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21.95843</v>
+      </c>
+      <c r="G59" t="n">
+        <v>33.98854</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.58805</v>
+      </c>
+      <c r="D60" t="n">
+        <v>15.6511</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.49976</v>
+      </c>
+      <c r="F60" t="n">
+        <v>21.92026</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.39478</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16.5143</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15.88196</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.10393</v>
+      </c>
+      <c r="F61" t="n">
+        <v>21.49391</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34.22073</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>16.64227</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15.85787</v>
+      </c>
+      <c r="E62" t="n">
+        <v>15.96574</v>
+      </c>
+      <c r="F62" t="n">
+        <v>21.20715</v>
+      </c>
+      <c r="G62" t="n">
+        <v>33.78551</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>16.59992</v>
+      </c>
+      <c r="D63" t="n">
+        <v>15.99498</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.40078</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.797</v>
+      </c>
+      <c r="G63" t="n">
+        <v>33.87295</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>16.56127</v>
+      </c>
+      <c r="D64" t="n">
+        <v>15.82203</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.45821</v>
+      </c>
+      <c r="F64" t="n">
+        <v>22.11797</v>
+      </c>
+      <c r="G64" t="n">
+        <v>34.05058</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>16.49346</v>
+      </c>
+      <c r="D65" t="n">
+        <v>15.53859</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.36304</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.77106</v>
+      </c>
+      <c r="G65" t="n">
+        <v>34.7265</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>16.53482</v>
+      </c>
+      <c r="D66" t="n">
+        <v>15.95087</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.16081</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21.20867</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34.5651</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>16.60406</v>
+      </c>
+      <c r="D67" t="n">
+        <v>15.82476</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.18979</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.69523</v>
+      </c>
+      <c r="G67" t="n">
+        <v>33.65365</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>16.61445</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.07876</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.14036</v>
+      </c>
+      <c r="F68" t="n">
+        <v>21.53215</v>
+      </c>
+      <c r="G68" t="n">
+        <v>33.92887</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>16.46516</v>
+      </c>
+      <c r="D69" t="n">
+        <v>15.83568</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.17488</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.86371</v>
+      </c>
+      <c r="G69" t="n">
+        <v>33.68965</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>16.71152</v>
+      </c>
+      <c r="D70" t="n">
+        <v>15.96779</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.20006</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.53831</v>
+      </c>
+      <c r="G70" t="n">
+        <v>34.73947</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>16.98686</v>
+      </c>
+      <c r="D71" t="n">
+        <v>15.52939</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.13014</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.84835</v>
+      </c>
+      <c r="G71" t="n">
+        <v>33.93461</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.45266</v>
+      </c>
+      <c r="D72" t="n">
+        <v>15.5764</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.28084</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.95674</v>
+      </c>
+      <c r="G72" t="n">
+        <v>33.72895</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.52738</v>
+      </c>
+      <c r="D73" t="n">
+        <v>15.77995</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.15567</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.67613</v>
+      </c>
+      <c r="G73" t="n">
+        <v>33.94656</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16.65759</v>
+      </c>
+      <c r="D74" t="n">
+        <v>15.85544</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.46338</v>
+      </c>
+      <c r="F74" t="n">
+        <v>21.06825</v>
+      </c>
+      <c r="G74" t="n">
+        <v>34.22893</v>
       </c>
     </row>
   </sheetData>
